--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_048.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_048.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CB563E9-D5B0-4DBF-866F-0DA7B81A2918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35801639-7803-4008-99D3-1F3F1B210725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -684,13 +684,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S04aH04,S01aH04,S04aH03,S03aH04,S06aH04,S01aH03,S05aH03,S03aH03,S05aH04,S06aH03,S02aH03</t>
+    <t>S01aH03,S05aH03,S05aH04,S06aH03,S04aH04,S01aH04,S04aH03,S02aH04,S03aH04,S06aH04,S02aH03,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S04aH07,S05aH05,S03aH02,S01aH05,S03aH06,S03aH07,S06aH05,S04aH02,S02aH01,S05aH02,S05aH06,S04aH05,S06aH01,S01aH07,S02aH07,S05aH01,S02aH05,S06aH07,S02aH02,S06aH06,S01aH06,S05aH07,S01aH02,S01aH01,S04aH01,S04aH06,S06aH02,S03aH01</t>
+    <t>S03aH01,S01aH06,S05aH07,S01aH02,S01aH05,S03aH06,S03aH07,S06aH05,S02aH01,S05aH02,S05aH06,S02aH06,S03aH05,S04aH07,S05aH05,S03aH02,S04aH05,S06aH01,S01aH07,S02aH07,S05aH01,S02aH05,S06aH07,S01aH01,S04aH01,S04aH06,S06aH02,S04aH02,S02aH02,S06aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH06,S03aH05,S04aH07,S05aH05,S03aH02,S01aH05,S03aH06,S03aH07,S06aH05,S04aH02,S02aH01,S05aH02,S05aH06,S04aH05,S06aH01,S01aH07,S02aH07,S05aH01,S02aH05,S06aH07,S02aH02,S06aH06,S01aH06,S05aH07,S01aH02,S01aH01,S04aH01,S04aH06,S06aH02,S03aH01</v>
+        <v>S03aH01,S01aH06,S05aH07,S01aH02,S01aH05,S03aH06,S03aH07,S06aH05,S02aH01,S05aH02,S05aH06,S02aH06,S03aH05,S04aH07,S05aH05,S03aH02,S04aH05,S06aH01,S01aH07,S02aH07,S05aH01,S02aH05,S06aH07,S01aH01,S04aH01,S04aH06,S06aH02,S04aH02,S02aH02,S06aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S04aH04,S01aH04,S04aH03,S03aH04,S06aH04,S01aH03,S05aH03,S03aH03,S05aH04,S06aH03,S02aH03</v>
+        <v>S01aH03,S05aH03,S05aH04,S06aH03,S04aH04,S01aH04,S04aH03,S02aH04,S03aH04,S06aH04,S02aH03,S03aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1413,7 +1413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFC0A9E-43C7-43AA-B781-7E0514FA12DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0C6948-9614-4E44-A20A-D318795DD6E2}">
   <dimension ref="A9:G17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1533,7 +1533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E1CBD3-DC91-4D70-BC38-B12471E3A342}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F692CB1F-A819-4291-8015-9964B38DED32}">
   <dimension ref="B9:O850"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28475,7 +28475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6988B66-43BD-4219-A6EF-041354F96E2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A685D2-0512-4560-A5AA-9ED218A8A6DF}">
   <dimension ref="B9:GB60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43588,7 +43588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A3310C-5563-4736-A888-6625F62C25AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E822C37E-AC5C-4881-BB24-1DCBE9D75B94}">
   <dimension ref="B9:E52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44206,7 +44206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2C9AF6-DCD9-46DC-B629-67718C7E42A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B54C431-1AF8-4BC0-BA3A-73E90E9E236B}">
   <dimension ref="B9:D94"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45157,7 +45157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BD8A1C-1916-49A5-AFC4-7F63A2498F36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1929C1D3-BB97-4149-9889-92147EC96A96}">
   <dimension ref="B9:D52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45646,7 +45646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D41539-390A-477D-AEE4-B02E7ABEDE21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECCBF2A-08C5-47E4-8854-24D1316D833B}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45706,7 +45706,7 @@
         <v>43</v>
       </c>
       <c r="D13">
-        <v>0.17874285714285715</v>
+        <v>0.17874285714285712</v>
       </c>
       <c r="E13" t="s">
         <v>222</v>
@@ -45790,7 +45790,7 @@
         <v>43</v>
       </c>
       <c r="D19">
-        <v>0.23489999999999994</v>
+        <v>0.23489999999999997</v>
       </c>
       <c r="E19" t="s">
         <v>222</v>
@@ -45874,7 +45874,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.16902857142857139</v>
+        <v>0.16902857142857144</v>
       </c>
       <c r="E25" t="s">
         <v>222</v>
@@ -46042,7 +46042,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.30129999999999996</v>
+        <v>0.30130000000000001</v>
       </c>
       <c r="E37" t="s">
         <v>222</v>
@@ -46378,7 +46378,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.26065714285714281</v>
+        <v>0.26065714285714287</v>
       </c>
       <c r="E61" t="s">
         <v>222</v>
@@ -46462,7 +46462,7 @@
         <v>43</v>
       </c>
       <c r="D67">
-        <v>0.2512571428571429</v>
+        <v>0.25125714285714285</v>
       </c>
       <c r="E67" t="s">
         <v>222</v>
@@ -46630,7 +46630,7 @@
         <v>43</v>
       </c>
       <c r="D79">
-        <v>0.24680000000000005</v>
+        <v>0.24679999999999999</v>
       </c>
       <c r="E79" t="s">
         <v>222</v>
@@ -46966,7 +46966,7 @@
         <v>43</v>
       </c>
       <c r="D103">
-        <v>0.25779999999999997</v>
+        <v>0.25780000000000003</v>
       </c>
       <c r="E103" t="s">
         <v>222</v>
@@ -47134,7 +47134,7 @@
         <v>43</v>
       </c>
       <c r="D115">
-        <v>0.28542857142857148</v>
+        <v>0.28542857142857142</v>
       </c>
       <c r="E115" t="s">
         <v>222</v>
@@ -47470,7 +47470,7 @@
         <v>43</v>
       </c>
       <c r="D139">
-        <v>0.26371428571428568</v>
+        <v>0.26371428571428573</v>
       </c>
       <c r="E139" t="s">
         <v>222</v>
@@ -47554,7 +47554,7 @@
         <v>43</v>
       </c>
       <c r="D145">
-        <v>0.22011428571428571</v>
+        <v>0.22011428571428573</v>
       </c>
       <c r="E145" t="s">
         <v>222</v>
@@ -47638,7 +47638,7 @@
         <v>43</v>
       </c>
       <c r="D151">
-        <v>0.24881428571428568</v>
+        <v>0.24881428571428571</v>
       </c>
       <c r="E151" t="s">
         <v>222</v>
